--- a/Categoría/MSPS_Categoría.xlsx
+++ b/Categoría/MSPS_Categoría.xlsx
@@ -833,13 +833,13 @@
         <v>0.3508787595244006</v>
       </c>
       <c r="C2" s="2">
-        <v>112.2262160580291</v>
+        <v>111.9612147751073</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>0.3937779547655862</v>
+        <v>0.3928481215513465</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1009,7 +1009,7 @@
         <v>6</v>
       </c>
       <c r="E12" s="2">
-        <v>4.452085588057913</v>
+        <v>4.452085588057914</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2029,7 +2029,7 @@
         <v>6</v>
       </c>
       <c r="E72" s="2">
-        <v>0.7110152669897477</v>
+        <v>0.7110152669897478</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2921,7 +2921,7 @@
         <v>129</v>
       </c>
       <c r="B125" s="2">
-        <v>8.592480762608204</v>
+        <v>8.592480762608202</v>
       </c>
       <c r="C125" s="2">
         <v>115.8092085278593</v>
